--- a/results/0916-all/长城沿线农牧区/tech_selected_summary.xlsx
+++ b/results/0916-all/长城沿线农牧区/tech_selected_summary.xlsx
@@ -286,232 +286,232 @@
     <t>左云县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>技术60</t>
-  </si>
-  <si>
-    <t>技术61</t>
-  </si>
-  <si>
-    <t>技术62</t>
-  </si>
-  <si>
-    <t>技术63</t>
-  </si>
-  <si>
-    <t>技术64</t>
-  </si>
-  <si>
-    <t>技术65</t>
-  </si>
-  <si>
-    <t>技术66</t>
-  </si>
-  <si>
-    <t>技术67</t>
-  </si>
-  <si>
-    <t>技术68</t>
-  </si>
-  <si>
-    <t>技术69</t>
-  </si>
-  <si>
-    <t>技术70</t>
-  </si>
-  <si>
-    <t>技术71</t>
-  </si>
-  <si>
-    <t>技术72</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Tech60</t>
+  </si>
+  <si>
+    <t>Tech61</t>
+  </si>
+  <si>
+    <t>Tech62</t>
+  </si>
+  <si>
+    <t>Tech63</t>
+  </si>
+  <si>
+    <t>Tech64</t>
+  </si>
+  <si>
+    <t>Tech65</t>
+  </si>
+  <si>
+    <t>Tech66</t>
+  </si>
+  <si>
+    <t>Tech67</t>
+  </si>
+  <si>
+    <t>Tech68</t>
+  </si>
+  <si>
+    <t>Tech69</t>
+  </si>
+  <si>
+    <t>Tech70</t>
+  </si>
+  <si>
+    <t>Tech71</t>
+  </si>
+  <si>
+    <t>Tech72</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 2821.14</t>
+    <t>2821.14</t>
   </si>
   <si>
     <t>Increasing byproduct_pig</t>
@@ -529,10 +529,10 @@
     <t>Acidification_pig</t>
   </si>
   <si>
-    <t>总经济成本: -3103030.61</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>-3103030.61</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>Increasing byproduct_beef cattle</t>
@@ -610,13 +610,13 @@
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 339654362.86</t>
+    <t>339654362.86</t>
   </si>
   <si>
     <t>artificial film cover_pig</t>
   </si>
   <si>
-    <t>总经济成本: 10303693.58</t>
+    <t>10303693.58</t>
   </si>
   <si>
     <t>Frequent removal_sheep&amp;goat</t>
@@ -649,7 +649,7 @@
     <t>irrigation (drip irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 29674432.18</t>
+    <t>29674432.18</t>
   </si>
   <si>
     <t>Nitrocompounds_dairy</t>
@@ -682,16 +682,16 @@
     <t>irrigation (AWD irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 98011626.78</t>
+    <t>98011626.78</t>
   </si>
   <si>
     <t>Zeolite_pig</t>
   </si>
   <si>
-    <t>总经济成本: 27773301.99</t>
-  </si>
-  <si>
-    <t>总经济成本: 7416226.65</t>
+    <t>27773301.99</t>
+  </si>
+  <si>
+    <t>7416226.65</t>
   </si>
   <si>
     <t>Organic acid_sheep &amp; goat</t>
@@ -772,10 +772,10 @@
     <t>irrigation (water-saving irrigation)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 271945234.42</t>
-  </si>
-  <si>
-    <t>总经济成本: 48409978.13</t>
+    <t>271945234.42</t>
+  </si>
+  <si>
+    <t>48409978.13</t>
   </si>
   <si>
     <t>Slatted floor vs Solid floor_dairy</t>
@@ -787,7 +787,7 @@
     <t>4R(Right type)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 233314010.31</t>
+    <t>233314010.31</t>
   </si>
   <si>
     <t>Frequent removal_dairy</t>
@@ -799,10 +799,10 @@
     <t>EEF(CRF)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 191647748.11</t>
-  </si>
-  <si>
-    <t>总经济成本: 54488383.22</t>
+    <t>191647748.11</t>
+  </si>
+  <si>
+    <t>54488383.22</t>
   </si>
   <si>
     <t>EEF(CRF)_rice</t>
@@ -811,28 +811,28 @@
     <t>4R(Right rate)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 241316438.05</t>
-  </si>
-  <si>
-    <t>总经济成本: 13097.90</t>
-  </si>
-  <si>
-    <t>总经济成本: 60502821.70</t>
-  </si>
-  <si>
-    <t>总经济成本: 23911460.59</t>
+    <t>241316438.05</t>
+  </si>
+  <si>
+    <t>13097.90</t>
+  </si>
+  <si>
+    <t>60502821.70</t>
+  </si>
+  <si>
+    <t>23911460.59</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 135169492.92</t>
-  </si>
-  <si>
-    <t>总经济成本: 2459320.94</t>
-  </si>
-  <si>
-    <t>总经济成本: 125187.18</t>
+    <t>135169492.92</t>
+  </si>
+  <si>
+    <t>2459320.94</t>
+  </si>
+  <si>
+    <t>125187.18</t>
   </si>
   <si>
     <t>Low protein diet_dairy</t>
@@ -850,10 +850,10 @@
     <t>incorporation_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 1534318373.79</t>
-  </si>
-  <si>
-    <t>总经济成本: 1189083.88</t>
+    <t>1534318373.79</t>
+  </si>
+  <si>
+    <t>1189083.88</t>
   </si>
   <si>
     <t>Slatted floor vs deep litter_pig</t>
@@ -865,52 +865,52 @@
     <t>biochar_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 1339664894.73</t>
-  </si>
-  <si>
-    <t>总经济成本: 101885592.39</t>
-  </si>
-  <si>
-    <t>总经济成本: 447294026.82</t>
+    <t>1339664894.73</t>
+  </si>
+  <si>
+    <t>101885592.39</t>
+  </si>
+  <si>
+    <t>447294026.82</t>
   </si>
   <si>
     <t>tillage management (zero tillage)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 39812854.16</t>
-  </si>
-  <si>
-    <t>总经济成本: 810808.50</t>
-  </si>
-  <si>
-    <t>总经济成本: 189684.50</t>
-  </si>
-  <si>
-    <t>总经济成本: 156659224.41</t>
-  </si>
-  <si>
-    <t>总经济成本: 2147138.20</t>
-  </si>
-  <si>
-    <t>总经济成本: 27016831.38</t>
-  </si>
-  <si>
-    <t>总经济成本: 16846307.04</t>
-  </si>
-  <si>
-    <t>总经济成本: 6220863.00</t>
+    <t>39812854.16</t>
+  </si>
+  <si>
+    <t>810808.50</t>
+  </si>
+  <si>
+    <t>189684.50</t>
+  </si>
+  <si>
+    <t>156659224.41</t>
+  </si>
+  <si>
+    <t>2147138.20</t>
+  </si>
+  <si>
+    <t>27016831.38</t>
+  </si>
+  <si>
+    <t>16846307.04</t>
+  </si>
+  <si>
+    <t>6220863.00</t>
   </si>
   <si>
     <t>Cover_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 57244099.82</t>
-  </si>
-  <si>
-    <t>总经济成本: 25942750.29</t>
-  </si>
-  <si>
-    <t>总经济成本: 80437802.06</t>
+    <t>57244099.82</t>
+  </si>
+  <si>
+    <t>25942750.29</t>
+  </si>
+  <si>
+    <t>80437802.06</t>
   </si>
 </sst>
 </file>
